--- a/pr_votes.xlsx
+++ b/pr_votes.xlsx
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4684090</v>
+        <v>4981973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1576440</v>
+        <v>1688008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1314367</v>
+        <v>1404850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>708602</v>
+        <v>764975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>332249</v>
+        <v>353616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>309074</v>
+        <v>323942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>156299</v>
+        <v>170758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150505</v>
+        <v>166279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69906</v>
+        <v>76096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56210</v>
+        <v>60654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41231</v>
+        <v>41939</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33587</v>
+        <v>37923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28985</v>
+        <v>29263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25229</v>
+        <v>27757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25174</v>
+        <v>27127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22222</v>
+        <v>23728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22118</v>
+        <v>23423</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17998</v>
+        <v>19796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13173</v>
+        <v>14305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12122</v>
+        <v>12707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9369</v>
+        <v>10026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7955</v>
+        <v>8539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -990,15 +990,15 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>नेपाल जनता पार्टी</t>
+          <t>स्वाभिमान पार्टी</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6642</v>
+        <v>7190</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2507.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2569.jpg</t>
         </is>
       </c>
     </row>
@@ -1009,15 +1009,15 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>राष्ट्रिय जनमुक्ति पार्टी</t>
+          <t>नेपाल जनता पार्टी</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6443</v>
+        <v>6989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2605.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2507.jpg</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6381</v>
+        <v>6844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1047,15 +1047,15 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>स्वाभिमान पार्टी</t>
+          <t>राष्ट्रिय जनमुक्ति पार्टी</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5892</v>
+        <v>6780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2569.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2605.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5390</v>
+        <v>5876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4761</v>
+        <v>5019</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4587</v>
+        <v>4852</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1123,15 +1123,15 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>नेपाल कम्युनिष्ट पार्टी मार्क्सवादी (पुष्पलाल)</t>
+          <t>राष्ट्रिय गौरव पार्टी</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4505</v>
+        <v>4801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2523.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2558.jpg</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>राष्ट्रिय गौरव पार्टी</t>
+          <t>नेपाल कम्युनिष्ट पार्टी मार्क्सवादी (पुष्पलाल)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4417</v>
+        <v>4753</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2558.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2523.jpg</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4354</v>
+        <v>4544</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1180,15 +1180,15 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>राष्ट्रिय उर्जाशील पार्टी, नेपाल</t>
+          <t>नेपाल कम्युनिष्ट पार्टी (संयुक्त)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4097</v>
+        <v>4402</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2534.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2601.jpg</t>
         </is>
       </c>
     </row>
@@ -1199,15 +1199,15 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>नेपाल कम्युनिष्ट पार्टी (संयुक्त)</t>
+          <t>राष्ट्रिय उर्जाशील पार्टी, नेपाल</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3890</v>
+        <v>4245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2601.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2534.jpg</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3824</v>
+        <v>4151</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3775</v>
+        <v>4021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3531</v>
+        <v>3851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2887</v>
+        <v>3113</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2592</v>
+        <v>2826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>बहुजन शक्ति पार्टी</t>
+          <t>जय मातृभूमि पार्टी</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2523</v>
+        <v>2697</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2536.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2510.jpg</t>
         </is>
       </c>
     </row>
@@ -1332,15 +1332,15 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>जय मातृभूमि पार्टी</t>
+          <t>बहुजन शक्ति पार्टी</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2516</v>
+        <v>2663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2510.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2536.jpg</t>
         </is>
       </c>
     </row>
@@ -1351,15 +1351,15 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>नेपाल जनमुक्ति पार्टी</t>
+          <t>प्रजातान्त्रिक पार्टी नेपाल</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2006</v>
+        <v>2106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2529.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2582.jpg</t>
         </is>
       </c>
     </row>
@@ -1370,15 +1370,15 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>प्रजातान्त्रिक पार्टी नेपाल</t>
+          <t>नेपाल जनमुक्ति पार्टी</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1930</v>
+        <v>2098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2582.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2529.jpg</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1876</v>
+        <v>1979</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1786</v>
+        <v>1913</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1427,15 +1427,15 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>पिपुल फर्ष्ट पार्टी</t>
+          <t>नेपाली काँग्रेस (वी.पी.)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1599</v>
+        <v>1707</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2552.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2509.jpg</t>
         </is>
       </c>
     </row>
@@ -1446,15 +1446,15 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>नेपाली काँग्रेस (वी.पी.)</t>
+          <t>पिपुल फर्ष्ट पार्टी</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1561</v>
+        <v>1703</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://result.election.gov.np/Images/symbol-hor-pa/2509.jpg</t>
+          <t>https://result.election.gov.np/Images/symbol-hor-pa/2552.jpg</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1500</v>
+        <v>1667</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1397</v>
+        <v>1522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1264</v>
+        <v>1389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1230</v>
+        <v>1313</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1162</v>
+        <v>1248</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1020</v>
+        <v>1093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>798</v>
+        <v>899</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>684</v>
+        <v>746</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>591</v>
+        <v>647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
